--- a/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
@@ -4333,7 +4333,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>특기품목</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -4364,17 +4364,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>4100000</v>
+        <v>3690000</v>
       </c>
       <c r="U32" t="n">
         <v>1820400</v>
       </c>
       <c r="V32" t="n">
-        <v>2279600</v>
+        <v>1869600</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -4396,8 +4396,16 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
@@ -7741,7 +7749,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -7765,7 +7773,7 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE85"/>
+  <dimension ref="A1:AE83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BW-2026-032</t>
+          <t>BW-2026-033</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BW260009</t>
+          <t xml:space="preserve">DPK365117536147  </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4062,15 +4062,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>텐트러스트</t>
+          <t>맥익스프레스 인터내셔날(주)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>潍坊市奎文区恒大名都26号楼 余涛 17589745505</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>河南省洛阳市老城区畔山兰溪2期 ATTN:小郑  tel: 17575006697</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>윤세형</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>항공(Air)</t>
@@ -4083,7 +4087,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>일반화물</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4118,19 +4122,15 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>300000</v>
+        <v>420000</v>
       </c>
       <c r="U30" t="n">
-        <v>220000</v>
+        <v>340000</v>
       </c>
       <c r="V30" t="n">
         <v>80000</v>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>윤세형 잡화컨테이너 진행</t>
-        </is>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BW-2026-033</t>
+          <t>BW-2026-034</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPK365117536147  </t>
+          <t>BW260011</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>맥익스프레스 인터내셔날(주)</t>
+          <t>리턴의원</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>河南省洛阳市老城区畔山兰溪2期 ATTN:小郑  tel: 17575006697</t>
+          <t>青岛市城阳区春阳路 92号 百富中心 32号楼 807室</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4220,19 +4220,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>65×61×124cm(1CTN)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.492 CBM</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -4241,22 +4241,26 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T31" t="n">
-        <v>420000</v>
+        <v>3690000</v>
       </c>
       <c r="U31" t="n">
-        <v>340000</v>
+        <v>1820400</v>
       </c>
       <c r="V31" t="n">
-        <v>80000</v>
-      </c>
-      <c r="W31" t="inlineStr"/>
+        <v>1869600</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>우든포장비 132,000원 별도 청구</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>정해균</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4283,22 +4287,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BW-2026-034</t>
+          <t>BW-2026-035</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BW260011</t>
+          <t>1ZRR43520338083680</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4308,22 +4312,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>리턴의원</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>青岛市城阳区春阳路 92号 百富中心 32号楼 807室</t>
+          <t xml:space="preserve">IMS/Andreina Mascobetto </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4333,29 +4337,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>5 박스 (CTN)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>65×61×124cm(1CTN)</t>
+          <t>41×30×40cm(5CTN)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.492 CBM</t>
+          <t>0.246 CBM</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="Q32" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -4364,26 +4368,22 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T32" t="n">
-        <v>3690000</v>
+        <v>1790000</v>
       </c>
       <c r="U32" t="n">
-        <v>1820400</v>
+        <v>1035000</v>
       </c>
       <c r="V32" t="n">
-        <v>1869600</v>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>우든포장비 132,000원 별도 청구</t>
-        </is>
-      </c>
+        <v>755000</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>정해균</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4396,16 +4396,8 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
@@ -4423,12 +4415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BW-2026-035</t>
+          <t>BW-2026-036</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1ZRR43520338083680</t>
+          <t>1ZRR43520330795738</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4448,7 +4440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS/Andreina Mascobetto </t>
+          <t>Wilian Ortiz Lima</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4473,24 +4465,24 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>41×30×40cm(5CTN)</t>
+          <t>49×47×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.246 CBM</t>
+          <t>0.051 CBM</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -4503,13 +4495,13 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>1790000</v>
+        <v>425000</v>
       </c>
       <c r="U33" t="n">
-        <v>1035000</v>
+        <v>235000</v>
       </c>
       <c r="V33" t="n">
-        <v>755000</v>
+        <v>190000</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
@@ -4546,12 +4538,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BW-2026-036</t>
+          <t>BW-2026-037</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1ZRR43520330795738</t>
+          <t>1ZRR43524238391041</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4571,12 +4563,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Wilian Ortiz Lima</t>
+          <t>Trang Phillip</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>주식회사 케이티글로발</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4591,7 +4583,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4601,19 +4593,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>49×47×22cm(1CTN)</t>
+          <t>49×36×46cm(1CTN)</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.051 CBM</t>
+          <t>0.082 CBM</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -4626,13 +4618,13 @@
         </is>
       </c>
       <c r="T34" t="n">
-        <v>425000</v>
+        <v>374000</v>
       </c>
       <c r="U34" t="n">
-        <v>235000</v>
+        <v>241812</v>
       </c>
       <c r="V34" t="n">
-        <v>190000</v>
+        <v>132188</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
@@ -4669,12 +4661,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BW-2026-037</t>
+          <t>BW-2026-038</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1ZRR43524238391041</t>
+          <t>1ZRR43524207297989</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4694,7 +4686,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Trang Phillip</t>
+          <t>DAMIAN RENATO JESUS MALO JUVER</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4719,24 +4711,24 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>12 박스 (CTN)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>49×36×46cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.082 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -4749,13 +4741,13 @@
         </is>
       </c>
       <c r="T35" t="n">
-        <v>374000</v>
+        <v>5214000</v>
       </c>
       <c r="U35" t="n">
-        <v>241812</v>
+        <v>4052098</v>
       </c>
       <c r="V35" t="n">
-        <v>132188</v>
+        <v>1161902</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
@@ -4787,17 +4779,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BW-2026-038</t>
+          <t>BW-2026-039</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1ZRR43524207297989</t>
+          <t>1ZRR43520339569305</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4812,17 +4804,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>뷰메디스</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER</t>
+          <t xml:space="preserve">K.her beauty clinic(Avanti plus)  </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>주식회사 케이티글로발</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4837,29 +4829,29 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40×31×29cm(1CTN)</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.037 CBM</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>237</v>
+        <v>10</v>
       </c>
       <c r="Q36" t="n">
-        <v>237</v>
+        <v>10</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -4872,13 +4864,13 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>5214000</v>
+        <v>390000</v>
       </c>
       <c r="U36" t="n">
-        <v>4052098</v>
+        <v>260000</v>
       </c>
       <c r="V36" t="n">
-        <v>1161902</v>
+        <v>130000</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
@@ -4915,12 +4907,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BW-2026-039</t>
+          <t>BW-2026-040</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1ZRR43520339569305</t>
+          <t>1ZRR43520304831381</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4940,7 +4932,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">K.her beauty clinic(Avanti plus)  </t>
+          <t>AVANTI</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4975,14 +4967,14 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.037 CBM</t>
+          <t>0.036 CBM</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4995,13 +4987,13 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>390000</v>
+        <v>312000</v>
       </c>
       <c r="U37" t="n">
-        <v>260000</v>
+        <v>185000</v>
       </c>
       <c r="V37" t="n">
-        <v>130000</v>
+        <v>127000</v>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
@@ -5038,12 +5030,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BW-2026-040</t>
+          <t>BW-2026-041</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1ZRR43520304831381</t>
+          <t>1ZRR43520318249315</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5058,12 +5050,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>뷰메디스</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>AVANTI</t>
+          <t>Danielle Stout</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5093,19 +5085,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>40×31×29cm(1CTN)</t>
+          <t>23×16×12cm(1CTN)</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.036 CBM</t>
+          <t>0.005 CBM</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -5114,17 +5106,17 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T38" t="n">
-        <v>312000</v>
+        <v>39000</v>
       </c>
       <c r="U38" t="n">
-        <v>185000</v>
+        <v>35000</v>
       </c>
       <c r="V38" t="n">
-        <v>127000</v>
+        <v>4000</v>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
@@ -5161,12 +5153,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BW-2026-041</t>
+          <t>BW-2026-042</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1ZRR43520318249315</t>
+          <t>1ZRR43520317439326</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5186,7 +5178,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Danielle Stout</t>
+          <t>Ana Ortiz</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5216,19 +5208,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>23×16×12cm(1CTN)</t>
+          <t>26×18×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.007 CBM</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -5241,13 +5233,13 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>39000</v>
+        <v>78000</v>
       </c>
       <c r="U39" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V39" t="n">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
@@ -5284,12 +5276,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BW-2026-042</t>
+          <t>BW-2026-043</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1ZRR43520317439326</t>
+          <t>1ZRR43520304641336</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5309,7 +5301,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Ana Ortiz</t>
+          <t>Zenith Edge</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5344,7 +5336,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.007 CBM</t>
+          <t>0.008 CBM</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -5407,12 +5399,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BW-2026-043</t>
+          <t>BW-2026-044</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1ZRR43520304641336</t>
+          <t>1ZRR43520314255342</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5432,7 +5424,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Zenith Edge</t>
+          <t>Jade Hall</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5462,12 +5454,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>26×18×15cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.008 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -5530,12 +5522,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BW-2026-044</t>
+          <t>BW-2026-045</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1ZRR43520314255342</t>
+          <t>1ZRR43520300681354</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5555,7 +5547,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Jade Hall</t>
+          <t xml:space="preserve">Dayanna Viquez </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5585,19 +5577,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>22×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -5610,13 +5602,13 @@
         </is>
       </c>
       <c r="T42" t="n">
-        <v>78000</v>
+        <v>39000</v>
       </c>
       <c r="U42" t="n">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="V42" t="n">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
@@ -5653,12 +5645,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BW-2026-045</t>
+          <t>BW-2026-046</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1ZRR43520300681354</t>
+          <t>1ZRR43520318319365</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5678,7 +5670,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dayanna Viquez </t>
+          <t>Zouzou Tang</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5776,12 +5768,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BW-2026-046</t>
+          <t>BW-2026-047</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1ZRR43520318319365</t>
+          <t>1ZRR43520301569377</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5801,7 +5793,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Zouzou Tang</t>
+          <t>Breanna Bryant</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5831,19 +5823,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>22×19×9cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -5856,13 +5848,13 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>39000</v>
+        <v>78000</v>
       </c>
       <c r="U44" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V44" t="n">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
@@ -5899,12 +5891,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BW-2026-047</t>
+          <t>BW-2026-049</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1ZRR43520301569377</t>
+          <t>1ZRR43520302505399</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5919,12 +5911,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Breanna Bryant</t>
+          <t>Maria Brenda</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5954,19 +5946,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>49×36×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.039 CBM</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -5975,17 +5967,17 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T45" t="n">
-        <v>78000</v>
+        <v>326720</v>
       </c>
       <c r="U45" t="n">
-        <v>60000</v>
+        <v>185000</v>
       </c>
       <c r="V45" t="n">
-        <v>18000</v>
+        <v>141720</v>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
@@ -6005,9 +5997,15 @@
       </c>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
+      <c r="AC45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6022,12 +6020,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BW-2026-049</t>
+          <t>BW-2026-050</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1ZRR43520302505399</t>
+          <t>1ZRR43520308991406</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6047,7 +6045,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maria Brenda</t>
+          <t>Trang Phillip</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6077,12 +6075,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>49×36×22cm(1CTN)</t>
+          <t>55×36×19cm(1CTN)</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.039 CBM</t>
+          <t>0.038 CBM</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -6151,12 +6149,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BW-2026-050</t>
+          <t>BW-2026-051</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1ZRR43520308991406</t>
+          <t>1ZRR43520302716938</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6176,12 +6174,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Trang Phillip</t>
+          <t>MC ALPHA GO/ Alemania Solano de la Torre</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6196,7 +6194,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -6206,23 +6204,23 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>55×36×19cm(1CTN)</t>
+          <t>49×35×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0.038 CBM</t>
+          <t>0.039 CBM</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
+          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6231,13 +6229,13 @@
         </is>
       </c>
       <c r="T47" t="n">
-        <v>326720</v>
+        <v>205560</v>
       </c>
       <c r="U47" t="n">
-        <v>185000</v>
+        <v>169200</v>
       </c>
       <c r="V47" t="n">
-        <v>141720</v>
+        <v>36360</v>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
@@ -6280,12 +6278,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BW-2026-051</t>
+          <t>BW-2026-052</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1ZRR43520302716938</t>
+          <t>1ZRR43520318689411</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6305,12 +6303,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MC ALPHA GO/ Alemania Solano de la Torre</t>
+          <t>Kristine Evangelista</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6325,7 +6323,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6335,23 +6333,23 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>49×35×22cm(1CTN)</t>
+          <t>27×19×17cm(1CTN)</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0.039 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
+          <t>📦 물류센터 입고 및 접수 완료</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6360,13 +6358,13 @@
         </is>
       </c>
       <c r="T48" t="n">
-        <v>205560</v>
+        <v>111680</v>
       </c>
       <c r="U48" t="n">
-        <v>169200</v>
+        <v>60000</v>
       </c>
       <c r="V48" t="n">
-        <v>36360</v>
+        <v>51680</v>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
@@ -6404,17 +6402,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BW-2026-052</t>
+          <t>BW-2026-053</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1ZRR43520318689411</t>
+          <t>1ZRR43520333795803</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6429,12 +6427,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>아코글로벌</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kristine Evangelista</t>
+          <t>Olga Voloshina</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6454,7 +6452,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -6464,38 +6462,38 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>27×19×17cm(1CTN)</t>
+          <t>37×37×25cm(1CTN)</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.035 CBM</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
+          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T49" t="n">
-        <v>111680</v>
+        <v>351000</v>
       </c>
       <c r="U49" t="n">
-        <v>60000</v>
+        <v>235000</v>
       </c>
       <c r="V49" t="n">
-        <v>51680</v>
+        <v>116000</v>
       </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
@@ -6515,15 +6513,9 @@
       </c>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6533,17 +6525,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BW-2026-053</t>
+          <t>BW-2026-054</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1ZRR43520333795803</t>
+          <t>BW260003</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6558,12 +6550,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>아코글로벌</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Olga Voloshina</t>
+          <t>Penny Korisko</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6593,23 +6585,23 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>37×37×25cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.035 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
+          <t>📦 물류센터 입고 및 접수 완료</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -6618,13 +6610,13 @@
         </is>
       </c>
       <c r="T50" t="n">
-        <v>351000</v>
+        <v>79680</v>
       </c>
       <c r="U50" t="n">
-        <v>235000</v>
+        <v>60000</v>
       </c>
       <c r="V50" t="n">
-        <v>116000</v>
+        <v>19680</v>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
@@ -6661,12 +6653,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BW-2026-054</t>
+          <t>BW-2026-055</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BW260003</t>
+          <t>BW260004</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6686,7 +6678,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Penny Korisko</t>
+          <t>Armita Azari</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6716,19 +6708,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>25×20×10cm(1CTN)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.005 CBM</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -6741,13 +6733,13 @@
         </is>
       </c>
       <c r="T51" t="n">
-        <v>79680</v>
+        <v>39840</v>
       </c>
       <c r="U51" t="n">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="V51" t="n">
-        <v>19680</v>
+        <v>4840</v>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
@@ -6784,12 +6776,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BW-2026-055</t>
+          <t>BW-2026-056</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BW260004</t>
+          <t>BW260005</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6809,7 +6801,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Armita Azari</t>
+          <t>Breanna Ross</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6839,12 +6831,12 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>25×20×10cm(1CTN)</t>
+          <t>21×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -6907,12 +6899,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BW-2026-056</t>
+          <t>BW-2026-057</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BW260005</t>
+          <t>BW260006</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6932,7 +6924,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Breanna Ross</t>
+          <t>Amanda Boyer</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6962,19 +6954,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>21×19×9cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -6987,13 +6979,13 @@
         </is>
       </c>
       <c r="T53" t="n">
-        <v>39840</v>
+        <v>79680</v>
       </c>
       <c r="U53" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V53" t="n">
-        <v>4840</v>
+        <v>19680</v>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
@@ -7030,12 +7022,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BW-2026-057</t>
+          <t>BW-2026-058</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BW260006</t>
+          <t>BW260007</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7055,7 +7047,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Amanda Boyer</t>
+          <t>Bella Glow Labs (Abigail Morales)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7148,17 +7140,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BW-2026-058</t>
+          <t>BW-2026-059</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BW260007</t>
+          <t>BW260008</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7173,12 +7165,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>텐트러스트</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bella Glow Labs (Abigail Morales)</t>
+          <t>Jun Cheong</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7198,7 +7190,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7208,19 +7200,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>45×31×16cm(1CTN)</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.022 CBM</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -7233,13 +7225,13 @@
         </is>
       </c>
       <c r="T55" t="n">
-        <v>79680</v>
+        <v>150000</v>
       </c>
       <c r="U55" t="n">
-        <v>60000</v>
+        <v>74000</v>
       </c>
       <c r="V55" t="n">
-        <v>19680</v>
+        <v>76000</v>
       </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
@@ -7252,16 +7244,26 @@
           <t>이상복</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>5332 Noel Drive Temple City, CA 91780</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>9099922845</t>
+        </is>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>3.45</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7276,12 +7278,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BW-2026-059</t>
+          <t>BW-2026-061</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BW260008</t>
+          <t>1ZRR43520326316852</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7296,12 +7298,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>텐트러스트</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Jun Cheong</t>
+          <t>Trisha Banusing</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7321,7 +7323,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -7331,12 +7333,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>45×31×16cm(1CTN)</t>
+          <t>36×36×18cm(1CTN)</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.022 CBM</t>
+          <t>0.023 CBM</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -7352,17 +7354,17 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T56" t="n">
-        <v>150000</v>
+        <v>219200</v>
       </c>
       <c r="U56" t="n">
-        <v>74000</v>
+        <v>110000</v>
       </c>
       <c r="V56" t="n">
-        <v>76000</v>
+        <v>109200</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
@@ -7378,22 +7380,22 @@
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>5332 Noel Drive Temple City, CA 91780</t>
+          <t>134 S Seneca Circle Anaheim California 92805 USA</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>9099922845</t>
+          <t>1 707-685-7724</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="57">
@@ -7409,17 +7411,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BW-2026-060</t>
+          <t>BW-2026-062</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BW260009</t>
+          <t>BW260011</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7429,22 +7431,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>에이블큐인터내셔널</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>杨小羊</t>
+          <t>Alex Arrieta Lopez</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7454,29 +7456,29 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>2 박스 (CTN)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>49×35×22cm(1CTN) / 49×46×28cm(1CTN)</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.102 CBM</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>332</v>
+        <v>21</v>
       </c>
       <c r="Q57" t="n">
-        <v>332</v>
+        <v>17</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -7485,19 +7487,23 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T57" t="n">
-        <v>15936000</v>
+        <v>792640</v>
       </c>
       <c r="U57" t="n">
-        <v>12948000</v>
+        <v>435000</v>
       </c>
       <c r="V57" t="n">
-        <v>2988000</v>
-      </c>
-      <c r="W57" t="inlineStr"/>
+        <v>357640</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>화장품 의약품</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -7505,26 +7511,28 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t xml:space="preserve">湖北省宜昌市秭归县茅坪镇建东大道海辣百川 </t>
-        </is>
-      </c>
-      <c r="AB57" t="n">
-        <v>19096164768</v>
+          <t>8589 NW 54TH ST MIAMI, FL 33166-3322</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>1 7862778309</t>
+        </is>
       </c>
       <c r="AC57" t="n">
-        <v>332</v>
+        <v>15.2</v>
       </c>
       <c r="AD57" t="n">
-        <v>332</v>
+        <v>15.2</v>
       </c>
       <c r="AE57" t="n">
-        <v>332</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="58">
@@ -7540,12 +7548,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BW-2026-061</t>
+          <t>BW-2026-063</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1ZRR43520326316852</t>
+          <t>1ZRR43520311856663</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7565,7 +7573,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Trisha Banusing</t>
+          <t>Rachelle Huemoeller</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7595,19 +7603,19 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>36×36×18cm(1CTN)</t>
+          <t>54×25×28cm(1CTN)</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>0.023 CBM</t>
+          <t>0.038 CBM</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -7620,15 +7628,19 @@
         </is>
       </c>
       <c r="T58" t="n">
-        <v>219200</v>
+        <v>326720</v>
       </c>
       <c r="U58" t="n">
-        <v>110000</v>
+        <v>210000</v>
       </c>
       <c r="V58" t="n">
-        <v>109200</v>
-      </c>
-      <c r="W58" t="inlineStr"/>
+        <v>116720</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>화장품 의약품</t>
+        </is>
+      </c>
       <c r="X58" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -7642,22 +7654,22 @@
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>134 S Seneca Circle Anaheim California 92805 USA</t>
+          <t>6279 Mahan drive, San Jose California 95123</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>1 707-685-7724</t>
+          <t>1 (408) 807-1185</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD58" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AE58" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="59">
@@ -7673,12 +7685,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BW-2026-062</t>
+          <t>BW-2026-064</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BW260011</t>
+          <t>1ZRR43520316271642</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7698,12 +7710,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Alex Arrieta Lopez</t>
+          <t>Jacquline A</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7718,29 +7730,29 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>49×35×22cm(1CTN) / 49×46×28cm(1CTN)</t>
+          <t>49×35×45cm(1CTN)</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>0.102 CBM</t>
+          <t>0.079 CBM</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -7749,23 +7761,19 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T59" t="n">
-        <v>792640</v>
+        <v>411120</v>
       </c>
       <c r="U59" t="n">
-        <v>435000</v>
+        <v>338400</v>
       </c>
       <c r="V59" t="n">
-        <v>357640</v>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>화장품 의약품</t>
-        </is>
-      </c>
+        <v>72720</v>
+      </c>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -7779,22 +7787,22 @@
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>8589 NW 54TH ST MIAMI, FL 33166-3322</t>
+          <t>555 Vwtrans Dr #201 Kyle,Tx 78640</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>1 7862778309</t>
+          <t>1 (512) 773-6361</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>15.2</v>
+        <v>17.3</v>
       </c>
       <c r="AD59" t="n">
-        <v>15.2</v>
+        <v>17.3</v>
       </c>
       <c r="AE59" t="n">
-        <v>15.2</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="60">
@@ -7810,12 +7818,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BW-2026-063</t>
+          <t>BW-2026-065</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1ZRR43520311856663</t>
+          <t>1ZRR43520316271642</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7835,12 +7843,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Rachelle Huemoeller</t>
+          <t>DAMIAN RENATO JESUS MALO JUVER</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7855,29 +7863,29 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>2 박스 (CTN)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>54×25×28cm(1CTN)</t>
+          <t>21×35×45cm(1CTN) / 49×35×45cm(1CTN)</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0.038 CBM</t>
+          <t>0.113 CBM</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -7890,17 +7898,17 @@
         </is>
       </c>
       <c r="T60" t="n">
-        <v>326720</v>
+        <v>1672320</v>
       </c>
       <c r="U60" t="n">
-        <v>210000</v>
+        <v>1305000</v>
       </c>
       <c r="V60" t="n">
-        <v>116720</v>
+        <v>367320</v>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>화장품 의약품</t>
+          <t>ups 1day 서비스요청건 kg당12000원 청구 완료</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -7916,22 +7924,22 @@
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>6279 Mahan drive, San Jose California 95123</t>
+          <t>14411-B Export Rd,LAREDO TEXAS, USA,ZIP CODE 78045</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>1 (408) 807-1185</t>
+          <t>1 8182189089</t>
         </is>
       </c>
       <c r="AC60" t="n">
-        <v>7.6</v>
+        <v>47.8</v>
       </c>
       <c r="AD60" t="n">
-        <v>7.6</v>
+        <v>47.8</v>
       </c>
       <c r="AE60" t="n">
-        <v>7.6</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="61">
@@ -7947,12 +7955,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BW-2026-064</t>
+          <t>BW-2026-066</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1ZRR43520316271642</t>
+          <t>BW260015</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7967,17 +7975,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Jacquline A</t>
+          <t>Kimberly Tapia</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7992,7 +8000,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -8002,19 +8010,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>49×35×45cm(1CTN)</t>
+          <t>35×28×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0.079 CBM</t>
+          <t>0.022 CBM</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -8023,17 +8031,17 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T61" t="n">
-        <v>411120</v>
+        <v>199200</v>
       </c>
       <c r="U61" t="n">
-        <v>338400</v>
+        <v>135000</v>
       </c>
       <c r="V61" t="n">
-        <v>72720</v>
+        <v>64200</v>
       </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
@@ -8049,22 +8057,22 @@
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>555 Vwtrans Dr #201 Kyle,Tx 78640</t>
+          <t>17320 Kingsbury St Granada Hills, CA 91344</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>1 (512) 773-6361</t>
+          <t>1-818-336-7713</t>
         </is>
       </c>
       <c r="AC61" t="n">
-        <v>17.3</v>
+        <v>4.11</v>
       </c>
       <c r="AD61" t="n">
-        <v>17.3</v>
+        <v>4.11</v>
       </c>
       <c r="AE61" t="n">
-        <v>17.3</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="62">
@@ -8075,22 +8083,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BW-2026-065</t>
+          <t>BW-2026-067</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1ZRR43520316271642</t>
+          <t>BW260016</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8100,22 +8108,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>텐트러스트</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER</t>
+          <t>余涛</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8125,29 +8133,29 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>21×35×45cm(1CTN) / 49×35×45cm(1CTN)</t>
+          <t>45×32×19cm(1CTN)</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0.113 CBM</t>
+          <t>0.028 CBM</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -8160,19 +8168,15 @@
         </is>
       </c>
       <c r="T62" t="n">
-        <v>1672320</v>
+        <v>150000</v>
       </c>
       <c r="U62" t="n">
-        <v>1305000</v>
+        <v>103600</v>
       </c>
       <c r="V62" t="n">
-        <v>367320</v>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>ups 1day 서비스요청건 kg당12000원 청구 완료</t>
-        </is>
-      </c>
+        <v>46400</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -8186,22 +8190,22 @@
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>14411-B Export Rd,LAREDO TEXAS, USA,ZIP CODE 78045</t>
+          <t>潍坊市奎文区恒大名都26号楼 余涛</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>1 8182189089</t>
+          <t>17589745505</t>
         </is>
       </c>
       <c r="AC62" t="n">
-        <v>47.8</v>
+        <v>4.86</v>
       </c>
       <c r="AD62" t="n">
-        <v>47.8</v>
+        <v>4.86</v>
       </c>
       <c r="AE62" t="n">
-        <v>47.8</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="63">
@@ -8212,22 +8216,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BW-2026-066</t>
+          <t>BW-2026-068</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BW260015</t>
+          <t>BW260017</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -8237,22 +8241,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>주식회사 조은로직스</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kimberly Tapia</t>
+          <t>河美兰</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8262,7 +8266,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -8272,19 +8276,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>35×28×22cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0.022 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -8293,17 +8297,17 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T63" t="n">
-        <v>199200</v>
+        <v>480000</v>
       </c>
       <c r="U63" t="n">
-        <v>135000</v>
+        <v>384000</v>
       </c>
       <c r="V63" t="n">
-        <v>64200</v>
+        <v>96000</v>
       </c>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr">
@@ -8313,28 +8317,28 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>17320 Kingsbury St Granada Hills, CA 91344</t>
+          <t>东莞市寮步镇和合园汇富中心A座313室  收件人</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>1-818-336-7713</t>
+          <t>13480021737</t>
         </is>
       </c>
       <c r="AC63" t="n">
-        <v>4.11</v>
+        <v>32</v>
       </c>
       <c r="AD63" t="n">
-        <v>4.11</v>
+        <v>32</v>
       </c>
       <c r="AE63" t="n">
-        <v>4.11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64">
@@ -8345,17 +8349,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BW-2026-067</t>
+          <t>BW-2026-069</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BW260016</t>
+          <t>BW260018</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -8370,17 +8374,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>텐트러스트</t>
+          <t>맥익스프레스 인터내셔날(주)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>余涛</t>
+          <t>金皓</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8400,24 +8404,24 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>45×32×19cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0.028 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>5</v>
+        <v>295</v>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>295</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -8430,15 +8434,19 @@
         </is>
       </c>
       <c r="T64" t="n">
-        <v>150000</v>
+        <v>5900000</v>
       </c>
       <c r="U64" t="n">
-        <v>103600</v>
+        <v>1475000</v>
       </c>
       <c r="V64" t="n">
-        <v>46400</v>
-      </c>
-      <c r="W64" t="inlineStr"/>
+        <v>4425000</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>인천시노 1톤차량 운임 50000원 비용지불</t>
+        </is>
+      </c>
       <c r="X64" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -8452,22 +8460,22 @@
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>潍坊市奎文区恒大名都26号楼 余涛</t>
+          <t>山东省威海市环翠区怡园街道抚顺路 高发大厦 主楼 C区 401</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17589745505</t>
+          <t>13906301025</t>
         </is>
       </c>
       <c r="AC64" t="n">
-        <v>4.86</v>
+        <v>295</v>
       </c>
       <c r="AD64" t="n">
-        <v>4.86</v>
+        <v>295</v>
       </c>
       <c r="AE64" t="n">
-        <v>4.86</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65">
@@ -8478,22 +8486,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BW-2026-068</t>
+          <t>BW-2026-070</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BW260017</t>
+          <t>BW260019</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8503,22 +8511,22 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>주식회사 조은로직스</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>河美兰</t>
+          <t xml:space="preserve">Gina Sylvester </t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8528,7 +8536,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -8538,19 +8546,19 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22×19×10cm(1CTN)</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.005 CBM</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -8563,13 +8571,13 @@
         </is>
       </c>
       <c r="T65" t="n">
-        <v>480000</v>
+        <v>39840</v>
       </c>
       <c r="U65" t="n">
-        <v>384000</v>
+        <v>35000</v>
       </c>
       <c r="V65" t="n">
-        <v>96000</v>
+        <v>4840</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr">
@@ -8585,22 +8593,22 @@
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>东莞市寮步镇和合园汇富中心A座313室  收件人</t>
+          <t>1093 Hawthorne Avenue, Beecher, IL 60401</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13480021737</t>
+          <t>1-708-595-3553</t>
         </is>
       </c>
       <c r="AC65" t="n">
-        <v>32</v>
+        <v>0.72</v>
       </c>
       <c r="AD65" t="n">
-        <v>32</v>
+        <v>0.72</v>
       </c>
       <c r="AE65" t="n">
-        <v>32</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="66">
@@ -8611,22 +8619,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BW-2026-069</t>
+          <t>BW-2026-071</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BW260018</t>
+          <t>BW260020</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -8636,12 +8644,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>맥익스프레스 인터내셔날(주)</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>金皓</t>
+          <t>Renay Scott</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8651,7 +8659,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8661,29 +8669,29 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34×20×20cm(1CTN)</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.014 CBM</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="Q66" t="n">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -8696,19 +8704,15 @@
         </is>
       </c>
       <c r="T66" t="n">
-        <v>5900000</v>
+        <v>119520</v>
       </c>
       <c r="U66" t="n">
-        <v>1475000</v>
+        <v>85000</v>
       </c>
       <c r="V66" t="n">
-        <v>4425000</v>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>인천시노 1톤차량 운임 50000원 비용지불</t>
-        </is>
-      </c>
+        <v>34520</v>
+      </c>
+      <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -8722,22 +8726,22 @@
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>山东省威海市环翠区怡园街道抚顺路 高发大厦 主楼 C区 401</t>
+          <t>619 Belleville Avenue Belleville, NJ 07109</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13906301025</t>
+          <t>1-862-336-5797</t>
         </is>
       </c>
       <c r="AC66" t="n">
-        <v>295</v>
+        <v>2.58</v>
       </c>
       <c r="AD66" t="n">
-        <v>295</v>
+        <v>2.58</v>
       </c>
       <c r="AE66" t="n">
-        <v>295</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="67">
@@ -8753,12 +8757,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BW-2026-070</t>
+          <t>BW-2026-072</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BW260019</t>
+          <t>BW260021</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8778,7 +8782,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gina Sylvester </t>
+          <t xml:space="preserve">Brenda A </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8808,7 +8812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>22×19×10cm(1CTN)</t>
+          <t>24×20×10cm(1CTN)</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -8855,22 +8859,22 @@
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>1093 Hawthorne Avenue, Beecher, IL 60401</t>
+          <t>11537 Lago De Garda Dr Austin, TX 78747</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>1-708-595-3553</t>
+          <t>1-512-489-7880</t>
         </is>
       </c>
       <c r="AC67" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -8886,12 +8890,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BW-2026-071</t>
+          <t>BW-2026-073</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BW260020</t>
+          <t>BW260022</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8906,12 +8910,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>아코글로벌</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Renay Scott</t>
+          <t>Mylene Marquez</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8941,19 +8945,19 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>34×20×20cm(1CTN)</t>
+          <t>28×28×28cm(1CTN)</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0.014 CBM</t>
+          <t>0.022 CBM</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -8966,13 +8970,13 @@
         </is>
       </c>
       <c r="T68" t="n">
-        <v>119520</v>
+        <v>199200</v>
       </c>
       <c r="U68" t="n">
-        <v>85000</v>
+        <v>110000</v>
       </c>
       <c r="V68" t="n">
-        <v>34520</v>
+        <v>89200</v>
       </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr">
@@ -8988,22 +8992,22 @@
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>619 Belleville Avenue Belleville, NJ 07109</t>
+          <t>Your Spa LLC 18832 Christina Avenue Cerritos, CA 90703 United States</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>1-862-336-5797</t>
+          <t>+1 (562) 412-4328</t>
         </is>
       </c>
       <c r="AC68" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
       <c r="AE68" t="n">
-        <v>2.58</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="69">
@@ -9019,12 +9023,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BW-2026-072</t>
+          <t>BW-2026-074</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BW260021</t>
+          <t>BW260023</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -9039,12 +9043,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>아코글로벌</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenda A </t>
+          <t>Jose Fernandez</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -9074,19 +9078,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>24×20×10cm(1CTN)</t>
+          <t>26×18×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.008 CBM</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -9099,13 +9103,13 @@
         </is>
       </c>
       <c r="T69" t="n">
-        <v>39840</v>
+        <v>79680</v>
       </c>
       <c r="U69" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V69" t="n">
-        <v>4840</v>
+        <v>19680</v>
       </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr">
@@ -9121,22 +9125,22 @@
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>11537 Lago De Garda Dr Austin, TX 78747</t>
+          <t>99 Van Buren St Newark NJ 07105 United States</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>1-512-489-7880</t>
+          <t>+1 (609) 331-6550</t>
         </is>
       </c>
       <c r="AC69" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AD69" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="AE69" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="70">
@@ -9152,12 +9156,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BW-2026-073</t>
+          <t>BW-2026-075</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BW260022</t>
+          <t>BW260024</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -9172,12 +9176,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>아코글로벌</t>
+          <t>뷰메디스</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Mylene Marquez</t>
+          <t>Opus beauty</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -9207,19 +9211,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>28×28×28cm(1CTN)</t>
+          <t>47×36×35cm(1CTN)</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>0.022 CBM</t>
+          <t>0.060 CBM</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -9232,13 +9236,13 @@
         </is>
       </c>
       <c r="T70" t="n">
-        <v>199200</v>
+        <v>517920</v>
       </c>
       <c r="U70" t="n">
-        <v>110000</v>
+        <v>285000</v>
       </c>
       <c r="V70" t="n">
-        <v>89200</v>
+        <v>232920</v>
       </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr">
@@ -9254,22 +9258,22 @@
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Your Spa LLC 18832 Christina Avenue Cerritos, CA 90703 United States</t>
+          <t>4465 Wilshire Blvd. #103 Los Angeles CA 90010 USA</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>+1 (562) 412-4328</t>
+          <t xml:space="preserve">+1 213 378 8996  </t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AD70" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AE70" t="n">
-        <v>3.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
@@ -9285,12 +9289,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BW-2026-074</t>
+          <t>BW-2026-076</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BW260023</t>
+          <t>BW260025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -9305,12 +9309,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>아코글로벌</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jose Fernandez</t>
+          <t>Lisa Czajko</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9340,19 +9344,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>26×18×15cm(1CTN)</t>
+          <t>47×37×34cm(1CTN)</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0.008 CBM</t>
+          <t>0.059 CBM</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -9365,13 +9369,13 @@
         </is>
       </c>
       <c r="T71" t="n">
-        <v>79680</v>
+        <v>478080</v>
       </c>
       <c r="U71" t="n">
-        <v>60000</v>
+        <v>285000</v>
       </c>
       <c r="V71" t="n">
-        <v>19680</v>
+        <v>193080</v>
       </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr">
@@ -9387,22 +9391,22 @@
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>99 Van Buren St Newark NJ 07105 United States</t>
+          <t>5 Toms way LaGrangeville NY 12540</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>+1 (609) 331-6550</t>
+          <t>1-347-739-2112</t>
         </is>
       </c>
       <c r="AC71" t="n">
-        <v>1.3</v>
+        <v>10.52</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.3</v>
+        <v>10.52</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.3</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="72">
@@ -9418,12 +9422,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BW-2026-075</t>
+          <t>BW-2026-077</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BW260024</t>
+          <t>BW260026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -9438,12 +9442,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>뷰메디스</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Opus beauty</t>
+          <t>Jayde Lysne</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9473,19 +9477,19 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>47×36×35cm(1CTN)</t>
+          <t>21×33×14cm(1CTN)</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0.060 CBM</t>
+          <t>0.010 CBM</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -9498,13 +9502,13 @@
         </is>
       </c>
       <c r="T72" t="n">
-        <v>517920</v>
+        <v>79680</v>
       </c>
       <c r="U72" t="n">
-        <v>285000</v>
+        <v>60000</v>
       </c>
       <c r="V72" t="n">
-        <v>232920</v>
+        <v>19680</v>
       </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr">
@@ -9514,28 +9518,28 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>4465 Wilshire Blvd. #103 Los Angeles CA 90010 USA</t>
+          <t>9 McDougall Dr Lincoln, ND 58504 USA</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 213 378 8996  </t>
+          <t>+17017718847</t>
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>11</v>
+        <v>1.3</v>
       </c>
       <c r="AD72" t="n">
-        <v>11</v>
+        <v>1.3</v>
       </c>
       <c r="AE72" t="n">
-        <v>11</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="73">
@@ -9546,17 +9550,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BW-2026-076</t>
+          <t>BW-2026-078</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BW260025</t>
+          <t>BW260027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -9576,7 +9580,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Lisa Czajko</t>
+          <t>Yahaira Monzon-Perez</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9601,24 +9605,24 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>3 박스 (CTN)</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>47×37×34cm(1CTN)</t>
+          <t>51×45×40cm(2CTN) / 36×35×25cm(1CTN)</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>0.059 CBM</t>
+          <t>0.220 CBM</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="Q73" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -9631,13 +9635,13 @@
         </is>
       </c>
       <c r="T73" t="n">
-        <v>478080</v>
+        <v>1872480</v>
       </c>
       <c r="U73" t="n">
-        <v>285000</v>
+        <v>1185000</v>
       </c>
       <c r="V73" t="n">
-        <v>193080</v>
+        <v>687480</v>
       </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr">
@@ -9647,28 +9651,28 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>5 Toms way LaGrangeville NY 12540</t>
+          <t>6036 Lowe Ln, Charlotte, NC, 28214</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>1-347-739-2112</t>
+          <t>1-(980) 729 – 3258</t>
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>10.52</v>
+        <v>46.19</v>
       </c>
       <c r="AD73" t="n">
-        <v>10.52</v>
+        <v>46.19</v>
       </c>
       <c r="AE73" t="n">
-        <v>10.52</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="74">
@@ -9679,17 +9683,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BW-2026-077</t>
+          <t>BW-2026-079</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BW260026</t>
+          <t>BW260028</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -9709,7 +9713,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Jayde Lysne</t>
+          <t xml:space="preserve">Elsa Paule   </t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9739,19 +9743,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>21×33×14cm(1CTN)</t>
+          <t>51×45×40cm(1CTN)</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>0.010 CBM</t>
+          <t>0.094 CBM</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -9764,13 +9768,13 @@
         </is>
       </c>
       <c r="T74" t="n">
-        <v>79680</v>
+        <v>756960</v>
       </c>
       <c r="U74" t="n">
-        <v>60000</v>
+        <v>410000</v>
       </c>
       <c r="V74" t="n">
-        <v>19680</v>
+        <v>346960</v>
       </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr">
@@ -9786,22 +9790,22 @@
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>9 McDougall Dr Lincoln, ND 58504 USA</t>
+          <t>94 Leonard st,2, Jersey City, new jersey, 07307</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>+17017718847</t>
+          <t>1-301-401-3096</t>
         </is>
       </c>
       <c r="AC74" t="n">
-        <v>1.3</v>
+        <v>15.57</v>
       </c>
       <c r="AD74" t="n">
-        <v>1.3</v>
+        <v>15.57</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.3</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="75">
@@ -9817,12 +9821,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BW-2026-078</t>
+          <t>BW-2026-080</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BW260027</t>
+          <t>BW260029</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -9842,7 +9846,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Yahaira Monzon-Perez</t>
+          <t>Samara Novaes</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9867,24 +9871,24 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>3 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>51×45×40cm(2CTN) / 36×35×25cm(1CTN)</t>
+          <t>33.5×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>0.220 CBM</t>
+          <t>0.094 CBM</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -9897,13 +9901,13 @@
         </is>
       </c>
       <c r="T75" t="n">
-        <v>1872480</v>
+        <v>79680</v>
       </c>
       <c r="U75" t="n">
-        <v>1185000</v>
+        <v>60000</v>
       </c>
       <c r="V75" t="n">
-        <v>687480</v>
+        <v>19680</v>
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
@@ -9919,22 +9923,22 @@
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>6036 Lowe Ln, Charlotte, NC, 28214</t>
+          <t>11230 Ranch Creek Ter, Apt 311 Bradenton, FL, 34211</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>1-(980) 729 – 3258</t>
+          <t>1-689-266-7610</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>46.19</v>
+        <v>0.83</v>
       </c>
       <c r="AD75" t="n">
-        <v>46.19</v>
+        <v>0.83</v>
       </c>
       <c r="AE75" t="n">
-        <v>46.19</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="76">
@@ -9950,12 +9954,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BW-2026-079</t>
+          <t>BW-2026-081</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BW260028</t>
+          <t>BW260030</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -9975,7 +9979,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsa Paule   </t>
+          <t>Sarah Larson</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -10005,19 +10009,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>51×45×40cm(1CTN)</t>
+          <t>22×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>0.094 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -10030,13 +10034,13 @@
         </is>
       </c>
       <c r="T76" t="n">
-        <v>756960</v>
+        <v>39840</v>
       </c>
       <c r="U76" t="n">
-        <v>410000</v>
+        <v>35000</v>
       </c>
       <c r="V76" t="n">
-        <v>346960</v>
+        <v>4840</v>
       </c>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr">
@@ -10052,22 +10056,22 @@
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>94 Leonard st,2, Jersey City, new jersey, 07307</t>
+          <t>18544 E Apricot Lane Queen Creek, AZ 85142</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>1-301-401-3096</t>
+          <t>1-602-369-0694</t>
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>15.57</v>
+        <v>0.44</v>
       </c>
       <c r="AD76" t="n">
-        <v>15.57</v>
+        <v>0.44</v>
       </c>
       <c r="AE76" t="n">
-        <v>15.57</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="77">
@@ -10083,12 +10087,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BW-2026-080</t>
+          <t>BW-2026-082</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BW260029</t>
+          <t>BW260031</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -10108,7 +10112,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Samara Novaes</t>
+          <t>Dr. Kyle Uhlich</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -10138,19 +10142,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>33.5×21×13cm(1CTN)</t>
+          <t>22×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0.094 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -10163,13 +10167,13 @@
         </is>
       </c>
       <c r="T77" t="n">
-        <v>79680</v>
+        <v>278880</v>
       </c>
       <c r="U77" t="n">
-        <v>60000</v>
+        <v>185000</v>
       </c>
       <c r="V77" t="n">
-        <v>19680</v>
+        <v>93880</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">
@@ -10185,22 +10189,22 @@
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>11230 Ranch Creek Ter, Apt 311 Bradenton, FL, 34211</t>
+          <t>403 SHADOW LANE SAPULPA, OK 74066</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>1-689-266-7610</t>
+          <t>1-405-985-1644</t>
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>0.83</v>
+        <v>6.4</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.83</v>
+        <v>6.4</v>
       </c>
       <c r="AE77" t="n">
-        <v>0.83</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="78">
@@ -10216,12 +10220,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BW-2026-081</t>
+          <t>BW-2026-083</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BW260030</t>
+          <t>BW260032</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -10241,7 +10245,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sarah Larson</t>
+          <t>Madison Berberich</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10271,19 +10275,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>22×19×9cm(1CTN)</t>
+          <t>33×21×14cm(1CTN)</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.010 CBM</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -10296,13 +10300,13 @@
         </is>
       </c>
       <c r="T78" t="n">
-        <v>39840</v>
+        <v>119520</v>
       </c>
       <c r="U78" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V78" t="n">
-        <v>4840</v>
+        <v>59520</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr">
@@ -10318,22 +10322,22 @@
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>18544 E Apricot Lane Queen Creek, AZ 85142</t>
+          <t>734 McCormick Ln Cincinnati, OH 45245 United States</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>1-602-369-0694</t>
+          <t>5136094841</t>
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
       <c r="AD78" t="n">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
       <c r="AE78" t="n">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="79">
@@ -10349,12 +10353,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BW-2026-082</t>
+          <t>BW-2026-084</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BW260031</t>
+          <t>BW260033</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -10369,12 +10373,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Dr. Kyle Uhlich</t>
+          <t>Bronislava Popovetsky</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -10399,24 +10403,24 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>2 박스 (CTN)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>22×19×9cm(1CTN)</t>
+          <t>49×35×38cm(2CTN)</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.134 CBM</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="Q79" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -10429,13 +10433,13 @@
         </is>
       </c>
       <c r="T79" t="n">
-        <v>278880</v>
+        <v>1007680</v>
       </c>
       <c r="U79" t="n">
-        <v>185000</v>
+        <v>585000</v>
       </c>
       <c r="V79" t="n">
-        <v>93880</v>
+        <v>422680</v>
       </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr">
@@ -10451,22 +10455,22 @@
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>403 SHADOW LANE SAPULPA, OK 74066</t>
+          <t>2549 Linden Street Bellmore, NY 11710</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>1-405-985-1644</t>
+          <t>1 (646) 407-9686</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>6.4</v>
+        <v>15.4</v>
       </c>
       <c r="AD79" t="n">
-        <v>6.4</v>
+        <v>15.4</v>
       </c>
       <c r="AE79" t="n">
-        <v>6.4</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="80">
@@ -10482,12 +10486,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BW-2026-083</t>
+          <t>BW-2026-085</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BW260032</t>
+          <t>BW260034</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -10502,12 +10506,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Madison Berberich</t>
+          <t>Maria Leonora A Dila</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10537,19 +10541,19 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>33×21×14cm(1CTN)</t>
+          <t>36×36×19cm(1CTN)</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0.010 CBM</t>
+          <t>0.025 CBM</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -10562,13 +10566,13 @@
         </is>
       </c>
       <c r="T80" t="n">
-        <v>119520</v>
+        <v>255040</v>
       </c>
       <c r="U80" t="n">
-        <v>60000</v>
+        <v>135000</v>
       </c>
       <c r="V80" t="n">
-        <v>59520</v>
+        <v>120040</v>
       </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr">
@@ -10584,22 +10588,22 @@
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>734 McCormick Ln Cincinnati, OH 45245 United States</t>
+          <t>31500 Grape St STE 3 Lake Elsinore, CA 92532</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>5136094841</t>
+          <t>1 714-512-1776</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD80" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="81">
@@ -10615,12 +10619,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BW-2026-084</t>
+          <t>BW-2026-086</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BW260033</t>
+          <t>BW260035</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -10640,7 +10644,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bronislava Popovetsky</t>
+          <t>Sharon Seng</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10665,24 +10669,24 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>49×35×38cm(2CTN)</t>
+          <t>49×36×23cm(1CTN)</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0.134 CBM</t>
+          <t>0.042 CBM</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="Q81" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -10695,13 +10699,13 @@
         </is>
       </c>
       <c r="T81" t="n">
-        <v>1007680</v>
+        <v>362560</v>
       </c>
       <c r="U81" t="n">
-        <v>585000</v>
+        <v>210000</v>
       </c>
       <c r="V81" t="n">
-        <v>422680</v>
+        <v>152560</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
@@ -10711,28 +10715,28 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2549 Linden Street Bellmore, NY 11710</t>
+          <t>921 Palo Cedro Dr Corona, California  92879</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>1 (646) 407-9686</t>
+          <t>1 (657) 527-2068</t>
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>15.4</v>
+        <v>7</v>
       </c>
       <c r="AD81" t="n">
-        <v>15.4</v>
+        <v>7</v>
       </c>
       <c r="AE81" t="n">
-        <v>15.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
@@ -10748,12 +10752,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BW-2026-085</t>
+          <t>BW-2026-087</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BW260034</t>
+          <t>BW260036</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -10773,12 +10777,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Maria Leonora A Dila</t>
+          <t>DAMIAN RENATO JESUS MALO JUVER 8182189089</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10793,29 +10797,29 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>19박스 (CTN)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>36×36×19cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>0.025 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>6</v>
+        <v>251</v>
       </c>
       <c r="Q82" t="n">
-        <v>5</v>
+        <v>249</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -10828,13 +10832,13 @@
         </is>
       </c>
       <c r="T82" t="n">
-        <v>255040</v>
+        <v>5732840</v>
       </c>
       <c r="U82" t="n">
-        <v>135000</v>
+        <v>4681200</v>
       </c>
       <c r="V82" t="n">
-        <v>120040</v>
+        <v>1051640</v>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr">
@@ -10844,28 +10848,24 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>31500 Grape St STE 3 Lake Elsinore, CA 92532</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>1 714-512-1776</t>
-        </is>
-      </c>
+          <t>DAMIAN RENATO JESUS MALO JUVER # B 14411 EXPORT RD LAREDO TX 78045-7945</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
-        <v>2.4</v>
+        <v>251</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.4</v>
+        <v>251</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.4</v>
+        <v>249</v>
       </c>
     </row>
     <row r="83">
@@ -10876,17 +10876,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BW-2026-086</t>
+          <t>BW-2026-088</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BW260035</t>
+          <t>BW260037</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -10901,12 +10901,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sharon Seng</t>
+          <t>Glenda King</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10936,19 +10936,19 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>49×36×23cm(1CTN)</t>
+          <t>27×19×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>0.042 CBM</t>
+          <t>0.008 CBM</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -10961,13 +10961,13 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>362560</v>
+        <v>79680</v>
       </c>
       <c r="U83" t="n">
-        <v>210000</v>
+        <v>60000</v>
       </c>
       <c r="V83" t="n">
-        <v>152560</v>
+        <v>19680</v>
       </c>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
@@ -10983,283 +10983,21 @@
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>921 Palo Cedro Dr Corona, California  92879</t>
+          <t>99 Glendale Park Rochester NY 14613</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>1 (657) 527-2068</t>
+          <t>1-585-730-9288</t>
         </is>
       </c>
       <c r="AC83" t="n">
-        <v>7</v>
+        <v>1.39</v>
       </c>
       <c r="AD83" t="n">
-        <v>7</v>
+        <v>1.39</v>
       </c>
       <c r="AE83" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>수출 (Export)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>BW-2026-087</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>BW260036</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>대한민국 (KOREA)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>넥서스파마 주식회사</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER 8182189089</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>유에스퀵</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>항공(Air)</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Door To Door</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>화장품</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>19박스 (CTN)</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>0.000 CBM</t>
-        </is>
-      </c>
-      <c r="P84" t="n">
-        <v>251</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>249</v>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>미수</t>
-        </is>
-      </c>
-      <c r="T84" t="n">
-        <v>5732840</v>
-      </c>
-      <c r="U84" t="n">
-        <v>4681200</v>
-      </c>
-      <c r="V84" t="n">
-        <v>1051640</v>
-      </c>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER # B 14411 EXPORT RD LAREDO TX 78045-7945</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr"/>
-      <c r="AC84" t="n">
-        <v>251</v>
-      </c>
-      <c r="AD84" t="n">
-        <v>251</v>
-      </c>
-      <c r="AE84" t="n">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>수출 (Export)</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>BW-2026-088</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>BW260037</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>대한민국 (KOREA)</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>글로우필메디앤코</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Glenda King</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>(주)카스익스프레스</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>항공(Air)</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Door To Door</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>보톡스</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>1 박스 (CTN)</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>27×19×15cm(1CTN)</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>0.008 CBM</t>
-        </is>
-      </c>
-      <c r="P85" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>2</v>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>미수</t>
-        </is>
-      </c>
-      <c r="T85" t="n">
-        <v>79680</v>
-      </c>
-      <c r="U85" t="n">
-        <v>60000</v>
-      </c>
-      <c r="V85" t="n">
-        <v>19680</v>
-      </c>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>99 Glendale Park Rochester NY 14613</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>1-585-730-9288</t>
-        </is>
-      </c>
-      <c r="AC85" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE85" t="n">
         <v>1.39</v>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
@@ -11012,7 +11012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,36 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>기타 잡비</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5710 대리비용 </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>미지급</t>
         </is>
@@ -12493,7 +12523,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "지급상태": "미지급", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 "}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
@@ -11012,7 +11012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11492,6 +11492,36 @@
         </is>
       </c>
       <c r="F16" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>109000</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>에이블쿠 인터내셔날 2명 83000원 대리비 26000원</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>미지급</t>
         </is>
@@ -12523,7 +12553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "지급상태": "미지급", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 "}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-27.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE83"/>
+  <dimension ref="A1:AE84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10999,6 +10999,139 @@
       </c>
       <c r="AE83" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BW-2026-089</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BW260038</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>张永学</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>윤세형</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0.000 CBM</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>12</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>수금완료</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>102000</v>
+      </c>
+      <c r="U84" t="n">
+        <v>84000</v>
+      </c>
+      <c r="V84" t="n">
+        <v>18000</v>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辽宁省大连市开发区马桥子街道赤峰街亿锋广场三期10号楼 </t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>18640817665</t>
+        </is>
+      </c>
+      <c r="AC84" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12553,7 +12686,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
         </is>
       </c>
     </row>
